--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 MOOSE MALE ONLY CWMU ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 MOOSE MALE ONLY CWMU ANY LEGAL WEAPON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -641,7 +646,8 @@
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -705,8 +711,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -774,8 +785,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -848,7 +864,8 @@
           <t>3.5</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -916,8 +933,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -985,8 +1007,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
@@ -1054,8 +1081,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
@@ -1123,8 +1155,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -1192,8 +1229,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -1261,8 +1303,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -1330,8 +1377,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1391,8 +1443,13 @@
       </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1456,8 +1513,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
